--- a/data/trans_orig/IP1009-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1009-Habitat-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4815</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5800</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191987</t>
+          <t>191984</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>207315</t>
+          <t>207327</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>401505</t>
+          <t>401532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>406674</t>
+          <t>407305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135658</t>
+          <t>135997</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203143</t>
+          <t>203825</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413661</t>
+          <t>413191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>677318</t>
+          <t>676771</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>717142</t>
+          <t>717149</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>722024</t>
+          <t>722023</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1396483</t>
+          <t>1396631</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402587</t>
+          <t>1402636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201457</t>
+          <t>200260</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>423380</t>
+          <t>423414</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3727</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203977</t>
+          <t>203355</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>414257</t>
+          <t>413672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>701906</t>
+          <t>702348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>745026</t>
+          <t>744680</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1450550</t>
+          <t>1450498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1455070</t>
+          <t>1454453</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,96%</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131125</t>
+          <t>130100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>278701</t>
+          <t>278416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4384</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>4409</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>219975</t>
+          <t>219715</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>426682</t>
+          <t>427197</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>153684</t>
+          <t>153693</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162344</t>
+          <t>161956</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317738</t>
+          <t>318117</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>322218</t>
+          <t>322215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5264</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5360</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202156</t>
+          <t>202022</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>407779</t>
+          <t>407796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>697209</t>
+          <t>698002</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>703602</t>
+          <t>703765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>738112</t>
+          <t>737975</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744170</t>
+          <t>744176</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1438717</t>
+          <t>1438793</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1446534</t>
+          <t>1446649</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1009-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1009-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -835,47 +835,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,74 +1065,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1377</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4585</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>634</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3179</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1377</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4815</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>210765</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>207557</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,84%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>311</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>194529</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>191984</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>191989</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>98,37%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>210765</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>207327</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,73%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>631</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>401532</t>
+          <t>401991</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>407305</t>
+          <t>406673</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>448</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1820</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2242</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2253</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>137369</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>135997</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>135575</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,68%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>460</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>285221</t>
+          <t>285055</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2797</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3999</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3478</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3948</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>207129</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>205027</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>207129</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>203825</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>579</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413191</t>
+          <t>413661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5550</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1081</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4250</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3695</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5551</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -2207,74 +2207,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>720628</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>717150</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>722021</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>679940</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>676771</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>677326</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,84%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>720628</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>717149</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>722023</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2099</t>
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1396631</t>
+          <t>1397099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1402636</t>
+          <t>1402639</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2782,47 +2782,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153098</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>136391</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,107 +3012,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5138</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4548</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1303</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4498</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1303</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3962</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>315</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>204095</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>200260</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>200850</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,37%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>636</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>423414</t>
+          <t>422878</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221977</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>317</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>205398</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3468,47 +3468,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154839</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,107 +3698,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3487</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>619</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3727</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3580</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3710</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>206463</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>203595</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>206463</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>203355</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>555</t>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>413672</t>
+          <t>413802</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207082</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207082</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,92 +4041,92 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3197</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4580</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4504</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1922</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>619</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3462</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1922</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -4154,74 +4154,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>747523</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>744945</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>705625</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>702348</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>702424</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,82%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>747523</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>744680</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2081</t>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1450498</t>
+          <t>1449877</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1454453</t>
+          <t>1454451</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>605</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3607</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2641</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>605</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3367</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>133102</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>130100</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>130690</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,55%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>381</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>278416</t>
+          <t>279142</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,107 +4959,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4398</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1452</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4644</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4349</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4409</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>222907</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>219961</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>222907</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>219715</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>664</t>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>427197</t>
+          <t>427257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>334</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>207247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,74 +5302,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4160</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>455</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2304</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2311</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>1,48%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1251</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4717</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>454</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165422</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>162513</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155542</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>153693</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>153686</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,71%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>98,52%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>165422</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>161956</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>504</t>
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318117</t>
+          <t>317559</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>322215</t>
+          <t>322216</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,92 +5645,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1525</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5398</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4587</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1525</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5758,74 +5758,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>205895</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>202022</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>202833</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,26%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,79%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>569</t>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>407796</t>
+          <t>407801</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>207420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5993,102 +5993,102 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6921</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>2585</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6369</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6577</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6869</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>5287</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>10690</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>5287</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>2566</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>10422</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -6101,107 +6101,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>742142</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>737923</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>744128</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1057</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>701786</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>698002</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>703765</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>697794</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>703617</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>742142</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>737975</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>744176</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,89%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1443928</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1438525</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1446743</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
         <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1443928</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>1438793</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>1446649</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
